--- a/data/trans_camb/P2C_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,69; 12,07</t>
+          <t>2,8; 12,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 12,44</t>
+          <t>2,02; 12,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,17; -7,33</t>
+          <t>-15,15; -7,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,57; 12,54</t>
+          <t>4,6; 12,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 3,8</t>
+          <t>-4,59; 4,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,33; -14,72</t>
+          <t>-21,37; -14,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,11; 11,45</t>
+          <t>5,12; 11,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 6,25</t>
+          <t>-0,45; 6,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-17,85; -12,93</t>
+          <t>-17,74; -12,8</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,21; 68,44</t>
+          <t>12,24; 67,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,92; 66,43</t>
+          <t>8,41; 65,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-67,03; -40,0</t>
+          <t>-67,29; -40,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,2; 47,24</t>
+          <t>14,78; 46,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 14,17</t>
+          <t>-15,16; 15,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-69,26; -55,1</t>
+          <t>-69,22; -54,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,92; 48,2</t>
+          <t>19,12; 47,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 25,69</t>
+          <t>-1,64; 26,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-66,6; -53,93</t>
+          <t>-66,18; -53,42</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,32; 17,09</t>
+          <t>8,27; 17,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 8,18</t>
+          <t>-0,57; 7,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-42,05; -34,03</t>
+          <t>-41,64; -34,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,15; 23,16</t>
+          <t>15,15; 23,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 5,78</t>
+          <t>-2,66; 5,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-47,5; -16,27</t>
+          <t>-47,5; -18,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,55; 18,72</t>
+          <t>12,88; 19,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 5,93</t>
+          <t>-0,37; 6,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-43,31; -23,44</t>
+          <t>-43,6; -24,99</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,43; 39,79</t>
+          <t>17,45; 40,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 18,75</t>
+          <t>-1,12; 18,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-88,34; -79,55</t>
+          <t>-88,48; -79,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,65; 40,73</t>
+          <t>24,66; 41,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 10,08</t>
+          <t>-4,35; 10,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-79,16; -27,17</t>
+          <t>-78,93; -30,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,09; 36,78</t>
+          <t>23,71; 37,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 11,67</t>
+          <t>-0,71; 11,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-81,54; -44,83</t>
+          <t>-81,71; -46,16</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,29; 29,99</t>
+          <t>12,17; 30,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 17,24</t>
+          <t>-0,93; 16,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-47,94; -34,21</t>
+          <t>-46,42; -34,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,13; 31,9</t>
+          <t>16,36; 31,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,66; 19,62</t>
+          <t>2,85; 18,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-56,22; -44,43</t>
+          <t>-55,46; -43,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,07; 28,64</t>
+          <t>16,99; 28,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,42; 15,95</t>
+          <t>3,53; 15,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-49,94; -40,75</t>
+          <t>-50,27; -40,94</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,76; 69,09</t>
+          <t>23,53; 70,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 40,61</t>
+          <t>-1,51; 40,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-89,49; -78,97</t>
+          <t>-89,25; -78,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26,28; 57,18</t>
+          <t>25,4; 56,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,14; 35,99</t>
+          <t>4,48; 33,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-86,49; -79,25</t>
+          <t>-86,44; -79,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,19; 57,86</t>
+          <t>29,07; 56,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,79; 32,21</t>
+          <t>6,33; 30,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-86,78; -80,51</t>
+          <t>-87,3; -80,78</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,1; 15,39</t>
+          <t>9,25; 15,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,19; 10,55</t>
+          <t>3,96; 9,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-32,07; -26,65</t>
+          <t>-31,91; -26,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,85; 18,58</t>
+          <t>12,84; 18,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,51; 8,54</t>
+          <t>2,19; 8,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-34,89; -12,71</t>
+          <t>-34,86; -12,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,06; 16,32</t>
+          <t>11,89; 16,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,83; 8,36</t>
+          <t>3,93; 8,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-32,74; -20,04</t>
+          <t>-32,92; -21,04</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>23,54; 43,34</t>
+          <t>23,77; 43,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,94; 30,13</t>
+          <t>10,19; 28,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-83,33; -75,45</t>
+          <t>-83,57; -75,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26,94; 41,93</t>
+          <t>27,23; 42,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,36; 19,41</t>
+          <t>4,66; 19,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-74,77; -27,64</t>
+          <t>-74,79; -27,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,21; 40,21</t>
+          <t>27,74; 40,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,9; 20,45</t>
+          <t>9,14; 20,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-77,3; -47,68</t>
+          <t>-77,63; -48,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-11,36</t>
+          <t>-11,22</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-17,81</t>
+          <t>-16,98</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-15,21</t>
+          <t>-14,67</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 12,19</t>
+          <t>2,74; 12,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 12,01</t>
+          <t>1,93; 12,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,15; -7,58</t>
+          <t>-15,14; -6,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,6; 12,49</t>
+          <t>4,05; 12,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 4,12</t>
+          <t>-4,52; 4,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,37; -14,43</t>
+          <t>-20,3; -13,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,12; 11,12</t>
+          <t>5,23; 11,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 6,22</t>
+          <t>-0,48; 6,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-17,74; -12,8</t>
+          <t>-17,2; -11,98</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-55,84%</t>
+          <t>-55,17%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-62,49%</t>
+          <t>-59,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-60,33%</t>
+          <t>-58,21%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,24; 67,12</t>
+          <t>12,47; 66,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,41; 65,22</t>
+          <t>8,26; 66,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-67,29; -40,31</t>
+          <t>-66,53; -38,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,78; 46,5</t>
+          <t>13,38; 48,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,16; 15,47</t>
+          <t>-14,77; 16,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-69,22; -54,87</t>
+          <t>-66,62; -51,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,12; 47,79</t>
+          <t>19,31; 49,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 26,18</t>
+          <t>-1,86; 25,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-66,18; -53,42</t>
+          <t>-64,16; -50,87</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-37,86</t>
+          <t>-36,19</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-38,26</t>
+          <t>-45,09</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-38,39</t>
+          <t>-40,93</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,27; 17,12</t>
+          <t>8,38; 17,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 7,81</t>
+          <t>-0,87; 8,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-41,64; -34,26</t>
+          <t>-39,86; -32,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,15; 23,53</t>
+          <t>15,67; 23,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 5,97</t>
+          <t>-2,54; 5,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-47,5; -18,76</t>
+          <t>-48,24; -41,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,88; 19,05</t>
+          <t>13,07; 19,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 6,0</t>
+          <t>-0,41; 6,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-43,6; -24,99</t>
+          <t>-43,48; -38,23</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-83,27%</t>
+          <t>-79,61%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-64,56%</t>
+          <t>-76,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-72,96%</t>
+          <t>-77,79%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,45; 40,48</t>
+          <t>17,95; 40,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 18,02</t>
+          <t>-1,84; 18,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-88,48; -79,73</t>
+          <t>-82,71; -76,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,66; 41,53</t>
+          <t>25,35; 40,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 10,43</t>
+          <t>-4,1; 10,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-78,93; -30,97</t>
+          <t>-78,55; -73,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,71; 37,57</t>
+          <t>24,14; 37,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 11,56</t>
+          <t>-0,89; 11,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-81,71; -46,16</t>
+          <t>-80,02; -75,59</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-40,88</t>
+          <t>-40,61</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-50,07</t>
+          <t>-49,48</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-45,44</t>
+          <t>-45,0</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,17; 30,04</t>
+          <t>12,01; 29,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 16,98</t>
+          <t>-1,91; 16,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-46,42; -34,12</t>
+          <t>-46,43; -33,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,36; 31,4</t>
+          <t>15,78; 31,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,85; 18,68</t>
+          <t>2,81; 18,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-55,46; -43,46</t>
+          <t>-55,79; -43,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,99; 28,7</t>
+          <t>17,32; 28,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 15,67</t>
+          <t>4,33; 15,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-50,27; -40,94</t>
+          <t>-49,26; -40,55</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-84,9%</t>
+          <t>-84,35%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-83,27%</t>
+          <t>-82,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-83,96%</t>
+          <t>-83,15%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,53; 70,28</t>
+          <t>23,78; 68,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 40,09</t>
+          <t>-4,06; 37,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-89,25; -78,95</t>
+          <t>-88,94; -78,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25,4; 56,91</t>
+          <t>24,58; 56,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,48; 33,43</t>
+          <t>4,37; 34,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-86,44; -79,51</t>
+          <t>-86,07; -78,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,07; 56,34</t>
+          <t>30,12; 56,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,33; 30,67</t>
+          <t>7,62; 30,55</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-87,3; -80,78</t>
+          <t>-85,82; -79,46</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-29,21</t>
+          <t>-28,06</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-29,11</t>
+          <t>-33,11</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-29,45</t>
+          <t>-30,95</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,25; 15,48</t>
+          <t>9,37; 15,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,96; 9,98</t>
+          <t>4,17; 10,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-31,91; -26,48</t>
+          <t>-30,61; -25,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,84; 18,79</t>
+          <t>12,7; 18,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,19; 8,47</t>
+          <t>2,38; 8,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-34,86; -12,99</t>
+          <t>-35,36; -30,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,89; 16,32</t>
+          <t>11,86; 16,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,93; 8,29</t>
+          <t>4,1; 8,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-32,92; -21,04</t>
+          <t>-32,65; -29,31</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-79,03%</t>
+          <t>-75,93%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-63,28%</t>
+          <t>-71,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-70,29%</t>
+          <t>-73,86%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>23,77; 43,04</t>
+          <t>24,38; 44,47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,19; 28,16</t>
+          <t>10,7; 29,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-83,57; -75,6</t>
+          <t>-78,9; -72,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27,23; 42,47</t>
+          <t>26,25; 41,05</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,66; 19,06</t>
+          <t>5,03; 18,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-74,79; -27,77</t>
+          <t>-74,24; -69,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,74; 40,12</t>
+          <t>27,66; 39,96</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,14; 20,5</t>
+          <t>9,78; 21,59</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-77,63; -48,25</t>
+          <t>-75,93; -71,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
